--- a/app/DeepKids_Science_Concept_Map.xlsx
+++ b/app/DeepKids_Science_Concept_Map.xlsx
@@ -853,12 +853,12 @@
       </c>
       <c r="E9" s="3" t="inlineStr">
         <is>
-          <t>–</t>
+          <t>L5 · Lesson 8 Soil and Crops</t>
         </is>
       </c>
       <c r="F9" s="3" t="inlineStr">
         <is>
-          <t>L2</t>
+          <t>L2, L5</t>
         </is>
       </c>
       <c r="G9" s="6" t="inlineStr">
@@ -1110,12 +1110,12 @@
       </c>
       <c r="E15" s="3" t="inlineStr">
         <is>
-          <t>–</t>
+          <t>L5 · Lesson 7 Life of Plants and Animals</t>
         </is>
       </c>
       <c r="F15" s="3" t="inlineStr">
         <is>
-          <t>L3, L4</t>
+          <t>L3, L4, L5</t>
         </is>
       </c>
       <c r="G15" s="6" t="inlineStr">
@@ -1152,12 +1152,13 @@
       </c>
       <c r="E16" s="3" t="inlineStr">
         <is>
-          <t>L3 · Lesson 6 Sun-Moon-Stars, Day-Night and Seasons</t>
+          <t>L3 · Lesson 6 Sun-Moon-Stars, Day-Night and Seasons
+L5 · Lesson 11 Solar System and Earth</t>
         </is>
       </c>
       <c r="F16" s="3" t="inlineStr">
         <is>
-          <t>L3, L4</t>
+          <t>L3, L4, L5</t>
         </is>
       </c>
       <c r="G16" s="6" t="inlineStr">
@@ -1230,7 +1231,7 @@
       </c>
       <c r="E18" s="3" t="inlineStr">
         <is>
-          <t>–</t>
+          <t>L5 · Lesson 5 The States of India and their Physical Features</t>
         </is>
       </c>
       <c r="F18" s="3" t="inlineStr">
@@ -1399,7 +1400,12 @@
           <t>L3 · Lesson 2 Our Social Environment
 L3 · Lesson 3 Our Festivals
 L3 · Lesson 11 National Identity
-L3 · Lesson 12 Our Social and Economic Environment</t>
+L3 · Lesson 12 Our Social and Economic Environment
+L5 · Lesson 1 India's Cultural and Natural Heritage: Its Conservation and Honour
+L5 · Lesson 2 Peace, Unity and Harmony in Indian Society
+L5 · Lesson 3 Our Social Issues
+L5 · Lesson 4 Our Freedom Struggle
+L5 · Lesson 6 Our Community and Public Administration</t>
         </is>
       </c>
       <c r="F22" s="3" t="inlineStr">
@@ -1759,7 +1765,8 @@
       </c>
       <c r="E30" s="3" t="inlineStr">
         <is>
-          <t>L3 · Lesson 5 Conservation of Environment</t>
+          <t>L3 · Lesson 5 Conservation of Environment
+L5 · Lesson 9 Conservation of Soil and Forests</t>
         </is>
       </c>
       <c r="F30" s="3" t="inlineStr">
@@ -1797,12 +1804,12 @@
       </c>
       <c r="E31" s="3" t="inlineStr">
         <is>
-          <t>–</t>
+          <t>L5 · Lesson 15 Garbage and Waste Disposal</t>
         </is>
       </c>
       <c r="F31" s="3" t="inlineStr">
         <is>
-          <t>L3</t>
+          <t>L3, L5</t>
         </is>
       </c>
       <c r="G31" s="6" t="inlineStr">
@@ -2036,12 +2043,12 @@
       </c>
       <c r="E37" s="3" t="inlineStr">
         <is>
-          <t>–</t>
+          <t>L5 · Lesson 13 Internal Organs of the Human Body</t>
         </is>
       </c>
       <c r="F37" s="3" t="inlineStr">
         <is>
-          <t>L1, L4</t>
+          <t>L1, L4, L5</t>
         </is>
       </c>
       <c r="G37" s="4" t="inlineStr">
@@ -2158,12 +2165,13 @@
       </c>
       <c r="E40" s="3" t="inlineStr">
         <is>
-          <t>L3 · Lesson 9 Care and cleanliness of external organs</t>
+          <t>L3 · Lesson 9 Care and cleanliness of external organs
+L5 · Lesson 14 Common Diseases: their Reasons, Prevention and Protection</t>
         </is>
       </c>
       <c r="F40" s="3" t="inlineStr">
         <is>
-          <t>L2, L3, L4</t>
+          <t>L2, L3, L4, L5</t>
         </is>
       </c>
       <c r="G40" s="6" t="inlineStr">
@@ -2250,7 +2258,8 @@
       </c>
       <c r="E42" s="3" t="inlineStr">
         <is>
-          <t>L3 · Lesson 8 Food</t>
+          <t>L3 · Lesson 8 Food
+L5 · Lesson 12 Food and Health</t>
         </is>
       </c>
       <c r="F42" s="3" t="inlineStr">
@@ -2367,7 +2376,7 @@
       </c>
       <c r="E45" s="3" t="inlineStr">
         <is>
-          <t>–</t>
+          <t>L5 · Lesson 10 Sources of Energy and their Importance</t>
         </is>
       </c>
       <c r="F45" s="3" t="inlineStr">
@@ -2431,7 +2440,7 @@
     <row r="5">
       <c r="A5" s="7" t="inlineStr">
         <is>
-          <t>Sources: NCERT Our Wondrous World 3–5 (2026-27), Cambridge Learner's Books 1–5 (Books 1 and 3 are 1st editions), NIOS Level A Environmental Studies.</t>
+          <t>Sources: NCERT Our Wondrous World 3–5 (2026-27), Cambridge Learner's Books 1–5 (Books 1 and 3 are 1st editions), NIOS Environmental Studies Levels A and B.</t>
         </is>
       </c>
     </row>
